--- a/uploaded_files/55555.xlsx
+++ b/uploaded_files/55555.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>эээээээээээээээээээээээээээээээ</t>
+          <t>Что означает саламандра в христианстве?</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
